--- a/output/Tables/2019/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.1651888028097898</v>
+        <v>0.1653204552422994</v>
       </c>
       <c r="B2">
-        <v>0.1734439321830256</v>
+        <v>0.1733648581652993</v>
       </c>
       <c r="C2">
-        <v>0.1810403131203978</v>
+        <v>0.1807695323400264</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.1653204552422994</v>
+        <v>0.1206215080444172</v>
       </c>
       <c r="B2">
-        <v>0.1733648581652993</v>
+        <v>0.1271312874973107</v>
       </c>
       <c r="C2">
-        <v>0.1807695323400264</v>
+        <v>0.1331095851999603</v>
       </c>
       <c r="D2">
         <v>1</v>
